--- a/Manuscript/Supplementary Tables/Appendix S1. Statistics.xlsx
+++ b/Manuscript/Supplementary Tables/Appendix S1. Statistics.xlsx
@@ -16,14 +16,14 @@
     <sheet name="FigS7B" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Fig5" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Fig6A-C_S10" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Fig6D-F" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Fig6D-I" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Other_DEGs" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t xml:space="preserve">Appendix S1. Statistical results</t>
   </si>
@@ -118,7 +118,7 @@
     <t xml:space="preserve">Fig. 6A-C, S10A-E: candidate neuroendocrine populations in 6_POA_Mixed</t>
   </si>
   <si>
-    <t xml:space="preserve">Fig6D-F</t>
+    <t xml:space="preserve">Fig6D-I</t>
   </si>
   <si>
     <t xml:space="preserve">Fig. 6D-I: steroid receptor-associated expression and promoter accessibility in 6_POA_Mixed</t>
@@ -823,10 +823,16 @@
     <t xml:space="preserve">gnrh1</t>
   </si>
   <si>
-    <t xml:space="preserve">Fig. 6D-I. Steroid receptor-associated expression (D-F) and promoter accessibility (G-I) in 6_POA_Mixed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lm on per-individual mean z-scored expression of genes with ESR2B, AR or PGR motifs in their promoters.</t>
+    <t xml:space="preserve">Fig. 6D-I. Steroid receptor-associated expression and promoter accessibility in 6_POA_Mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lm on per-individual mean z-scores of genes with ESR2B, AR or PGR motifs in their promoters: expression (6D, 6F, 6H) and promoter accessibility (6E, 6G, 6I).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig. 6D</t>
   </si>
   <si>
     <t xml:space="preserve">ESR2B-associated expression</t>
@@ -835,43 +841,49 @@
     <t xml:space="preserve">lm(mean_esr2b ~ Phase)</t>
   </si>
   <si>
+    <t xml:space="preserve">Fig. 6E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESR2B-associated accessibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lm(mean_esr2b_acc ~ Phase)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig. 6F</t>
+  </si>
+  <si>
     <t xml:space="preserve">AR-associated expression</t>
   </si>
   <si>
     <t xml:space="preserve">lm(mean_ar ~ Phase)</t>
   </si>
   <si>
+    <t xml:space="preserve">Fig. 6G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR-associated accessibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lm(mean_ar_acc ~ Phase)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig. 6H</t>
+  </si>
+  <si>
     <t xml:space="preserve">PGR-associated expression</t>
   </si>
   <si>
     <t xml:space="preserve">lm(mean_pgr ~ Phase)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fig. 6G-I: promoter accessibility of the same receptor-specific gene sets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lm on per-individual mean z-scored promoter accessibility (updatedcluster_6_..._ACCESSIBILITY_ZSCORES.csv).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESR2B-associated accessibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lm(mean_esr2b_acc ~ Phase)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AR-associated accessibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lm(mean_ar_acc ~ Phase)</t>
+    <t xml:space="preserve">Fig. 6I</t>
   </si>
   <si>
     <t xml:space="preserve">PGR-associated accessibility</t>
   </si>
   <si>
     <t xml:space="preserve">lm(mean_pgr_acc ~ Phase)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig. 6G-I: means by phase</t>
   </si>
   <si>
     <t xml:space="preserve">Other DEGs cited in the text</t>
@@ -3483,15 +3495,16 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="153.4075" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="26.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="135.6175" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="30.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="12.4975" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="21.9275" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="12.4975" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="12.4975" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21.9275" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="12.4975" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="12.4975" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="12.4975" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3511,241 +3524,310 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C6" s="7" t="n">
+        <v>270</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>4.63593597430577</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="E6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="7" t="n">
         <v>0.0258143124548248</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="7" t="n">
         <v>0.00827912671187644</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="I6" s="7" t="n">
         <v>0.256239582436876</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="J6" s="7" t="n">
         <v>0.0692171466904977</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>1.58429088683031</v>
-      </c>
-      <c r="D7" s="8" t="n">
+        <v>273</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>4.53429434204922</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="F7" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F7" s="7" t="n">
-        <v>0.235635112427355</v>
-      </c>
       <c r="G7" s="7" t="n">
-        <v>0.100423352180714</v>
+        <v>0.0275372637338781</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.243336474573349</v>
+        <v>0.101584955389163</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.558245143657805</v>
+        <v>0.24702315470831</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.00840586662695981</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="C8" s="7" t="n">
+        <v>276</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1.58429088683031</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.235635112427355</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.100423352180714</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.243336474573349</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.558245143657805</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2.62807077860121</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0.103058636467227</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>0.148691553636253</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.50505214937989</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0.038381865536101</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" s="7" t="n">
         <v>4.58238339226407</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="E10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="F10" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G10" s="7" t="n">
         <v>0.0267064757925928</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <v>0.00898969924979666</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="I10" s="7" t="n">
         <v>0.309582479884486</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="J10" s="7" t="n">
         <v>0.0587948046699056</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2.40301228471266</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.122305786635345</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0.23235445546219</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.381194857576141</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.0437884664740238</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>-0.0701029006514769</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>0.0686824476737086</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>0.00726754554747338</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0.0336672763886356</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0.0454580469563802</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.0269220231194271</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="D16" s="7" t="n">
         <v>-0.0754614725644326</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="E16" s="7" t="n">
         <v>0.0427909377074291</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="F16" s="8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="D17" s="7" t="n">
         <v>-0.0203934826345837</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>0.0285602214222746</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="F17" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="D18" s="7" t="n">
         <v>0.0706994454557497</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="E18" s="7" t="n">
         <v>0.0282133208695904</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="F18" s="8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3754,15 +3836,18 @@
         <v>272</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="7" t="n">
-        <v>-0.0602330462374897</v>
-      </c>
       <c r="D19" s="7" t="n">
-        <v>0.0453042978088317</v>
-      </c>
-      <c r="E19" s="8" t="n">
+        <v>-0.00604469135310768</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>0.0475669687368172</v>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3771,15 +3856,18 @@
         <v>272</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>-0.018002771250449</v>
-      </c>
       <c r="D20" s="7" t="n">
-        <v>0.0183148237035552</v>
-      </c>
-      <c r="E20" s="8" t="n">
+        <v>-0.0708491961766496</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0.0218157822589231</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3788,316 +3876,258 @@
         <v>272</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>0.0638794022806209</v>
-      </c>
       <c r="D21" s="7" t="n">
-        <v>0.0163792765373466</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>6</v>
+        <v>0.0911789448895453</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>0.045643649976525</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>-0.0701029006514769</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0.0686824476737086</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0.00726754554747338</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>0.0336672763886356</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>274</v>
+      <c r="A24" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.0454580469563802</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0.0269220231194271</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="s">
-        <v>275</v>
+      <c r="A25" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>-0.0115776702781211</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>0.0475860810680719</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>47</v>
+      <c r="A26" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>-0.0481864513935353</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0.0305166514701369</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>4.53429434204922</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>0.0275372637338781</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>0.101584955389163</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>0.24702315470831</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>0.00840586662695981</v>
+        <v>279</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0.072957169370641</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>0.037390522450265</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>2.62807077860121</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>0.103058636467227</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>0.148691553636253</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>0.50505214937989</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>0.038381865536101</v>
+        <v>282</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>-0.0602330462374897</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0.0453042978088317</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>-0.018002771250449</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>0.0183148237035552</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C29" s="7" t="n">
-        <v>2.40301228471266</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>0.122305786635345</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>0.23235445546219</v>
-      </c>
-      <c r="H29" s="7" t="n">
-        <v>0.381194857576141</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>0.0437884664740238</v>
+      <c r="B30" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.0638794022806209</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0.0163792765373466</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>-0.0027573983486353</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>0.0486928865941269</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="s">
-        <v>282</v>
+      <c r="A32" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>-0.0552850920829634</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0.0232028899182088</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>-0.0115776702781211</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0.0475860810680719</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="7" t="n">
-        <v>-0.0481864513935353</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>0.0305166514701369</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B36" s="6" t="s">
+      <c r="A33" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>0.072957169370641</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0.037390522450265</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>-0.00604469135310768</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>0.0475669687368172</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>-0.0708491961766496</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0.0218157822589231</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>0.0911789448895453</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>0.045643649976525</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>-0.0027573983486353</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0.0486928865941269</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>-0.0552850920829634</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>0.0232028899182088</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="7" t="n">
+      <c r="D33" s="7" t="n">
         <v>0.0723861185043957</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="E33" s="7" t="n">
         <v>0.0523244630471307</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="F33" s="8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4131,12 +4161,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
@@ -4193,13 +4223,13 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>22.2153050003675</v>
@@ -4265,10 +4295,10 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>67</v>
@@ -4285,10 +4315,10 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>68</v>
@@ -4305,10 +4335,10 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>41</v>
